--- a/Entrega 02/Arratia_Cobertura_mediatica_database/cobertura medios.xlsx
+++ b/Entrega 02/Arratia_Cobertura_mediatica_database/cobertura medios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/carolina_olave_uc_cl/Documents/7mo semestre/Narración gráfica de no ficción/Proyecto-Arratia-Bravo-Finkenberger/Entrega 02/Arratia_Cobertura_mediatica_database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="207" documentId="8_{A44EB21C-D202-4B6E-8B3A-F64D7E198FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AEF376B-8A85-4694-A7CD-D3D4808D5344}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="8_{A44EB21C-D202-4B6E-8B3A-F64D7E198FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCE6A4CE-AF42-4B68-A600-B5794DA45208}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{5617F6F5-E541-42D6-AF55-9597509312F3}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{5617F6F5-E541-42D6-AF55-9597509312F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="3" r:id="rId1"/>
@@ -416,16 +416,16 @@
     <t>caracol terrestre Tornatellina</t>
   </si>
   <si>
-    <t>Mención N. Científico</t>
-  </si>
-  <si>
-    <t>Mención N. Común</t>
-  </si>
-  <si>
     <t>Mención nacional</t>
   </si>
   <si>
     <t>Mención regional</t>
+  </si>
+  <si>
+    <t>Usa N. Científico</t>
+  </si>
+  <si>
+    <t>Usa N. Común</t>
   </si>
 </sst>
 </file>
@@ -494,8 +494,8 @@
     <tableColumn id="2" xr3:uid="{D12C8A28-44BD-4FDC-AE75-BA1C64FD3D76}" name="Nombre científico "/>
     <tableColumn id="3" xr3:uid="{5FD2AE46-9541-440A-901F-E328FE474AF7}" name="Nombre común"/>
     <tableColumn id="4" xr3:uid="{9D94CF3B-E776-4470-9B80-935EA4AB088E}" name="Clase"/>
-    <tableColumn id="5" xr3:uid="{76FD7BBB-E817-4A87-8A0F-374E5C1A4875}" name="Mención N. Científico"/>
-    <tableColumn id="13" xr3:uid="{3D0CC132-8F95-49D3-A61F-98BEAD9D8D16}" name="Mención N. Común"/>
+    <tableColumn id="5" xr3:uid="{76FD7BBB-E817-4A87-8A0F-374E5C1A4875}" name="Usa N. Científico"/>
+    <tableColumn id="13" xr3:uid="{3D0CC132-8F95-49D3-A61F-98BEAD9D8D16}" name="Usa N. Común"/>
     <tableColumn id="6" xr3:uid="{FA6967FF-3902-4A8C-915D-15C025F76AD4}" name="Mención nacional"/>
     <tableColumn id="7" xr3:uid="{91C979A9-CDDC-48F6-AAAB-2029D6C53C93}" name="Mención regional"/>
     <tableColumn id="12" xr3:uid="{EDC1753B-0323-4A81-9585-86B6CFC0A5F6}" name="Es carismático"/>
@@ -853,16 +853,16 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" t="s">
         <v>126</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>127</v>
-      </c>
-      <c r="G1" t="s">
-        <v>128</v>
-      </c>
-      <c r="H1" t="s">
-        <v>129</v>
       </c>
       <c r="I1" t="s">
         <v>3</v>

--- a/Entrega 02/Arratia_Cobertura_mediatica_database/cobertura medios.xlsx
+++ b/Entrega 02/Arratia_Cobertura_mediatica_database/cobertura medios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/carolina_olave_uc_cl/Documents/7mo semestre/Narración gráfica de no ficción/Proyecto-Arratia-Bravo-Finkenberger/Entrega 02/Arratia_Cobertura_mediatica_database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="8_{A44EB21C-D202-4B6E-8B3A-F64D7E198FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCE6A4CE-AF42-4B68-A600-B5794DA45208}"/>
+  <xr:revisionPtr revIDLastSave="254" documentId="8_{A44EB21C-D202-4B6E-8B3A-F64D7E198FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C2B3AC0-95E4-446F-A5FF-55D47CFD14A3}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{5617F6F5-E541-42D6-AF55-9597509312F3}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{5617F6F5-E541-42D6-AF55-9597509312F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="380">
   <si>
     <t xml:space="preserve">Nombre científico </t>
   </si>
@@ -416,23 +416,774 @@
     <t>caracol terrestre Tornatellina</t>
   </si>
   <si>
-    <t>Mención nacional</t>
-  </si>
-  <si>
-    <t>Mención regional</t>
-  </si>
-  <si>
     <t>Usa N. Científico</t>
   </si>
   <si>
     <t>Usa N. Común</t>
+  </si>
+  <si>
+    <t>Acalodegma vidali</t>
+  </si>
+  <si>
+    <t>Aegla bahamondei</t>
+  </si>
+  <si>
+    <t>Aegla concepcionensis</t>
+  </si>
+  <si>
+    <t>Aegla expansa</t>
+  </si>
+  <si>
+    <t>Aegla laevis</t>
+  </si>
+  <si>
+    <t>Aegla occidentalis</t>
+  </si>
+  <si>
+    <t>Aegla papudo</t>
+  </si>
+  <si>
+    <t>Allograpta robinsoniana</t>
+  </si>
+  <si>
+    <t>Alsodes cantillanensis</t>
+  </si>
+  <si>
+    <t>Alsodes valdiviensis</t>
+  </si>
+  <si>
+    <t>Alyma quiriquinaensis</t>
+  </si>
+  <si>
+    <t>Americobdella valdiviana</t>
+  </si>
+  <si>
+    <t>Amphidoxa arctispira</t>
+  </si>
+  <si>
+    <t>Amphidoxa ceroides</t>
+  </si>
+  <si>
+    <t>Amphidoxa helicophantoides</t>
+  </si>
+  <si>
+    <t>Amphidoxa marmorella</t>
+  </si>
+  <si>
+    <t>Amphidoxa pusio</t>
+  </si>
+  <si>
+    <t>Amphidoxa quadrata</t>
+  </si>
+  <si>
+    <t>Amphidoxa selkirki</t>
+  </si>
+  <si>
+    <t>Amphidoxa tessellata</t>
+  </si>
+  <si>
+    <t>Aplochiton zebra</t>
+  </si>
+  <si>
+    <t>Apterodorcus tristis</t>
+  </si>
+  <si>
+    <t>Basilichthys semotilus</t>
+  </si>
+  <si>
+    <t>Bolborhinum trilobulicorne</t>
+  </si>
+  <si>
+    <t>Brachistosternus cepedai</t>
+  </si>
+  <si>
+    <t>Bullockia maldonadoi</t>
+  </si>
+  <si>
+    <t>Callyntra cantillana</t>
+  </si>
+  <si>
+    <t>Callyntra multicosta</t>
+  </si>
+  <si>
+    <t>Callyntra penai</t>
+  </si>
+  <si>
+    <t>Callyntra planiuscula</t>
+  </si>
+  <si>
+    <t>Charopa involuta</t>
+  </si>
+  <si>
+    <t>Charopa masafuerae</t>
+  </si>
+  <si>
+    <t>Chinchilla lanigera</t>
+  </si>
+  <si>
+    <t>Cnemalobus hirsutus</t>
+  </si>
+  <si>
+    <t>Cnemalobus nuria</t>
+  </si>
+  <si>
+    <t>Conognatha azarae fisheri</t>
+  </si>
+  <si>
+    <t>Conognatha leechi</t>
+  </si>
+  <si>
+    <t>Diplomystes camposensis</t>
+  </si>
+  <si>
+    <t>Diplomystes nahuelbutaensis</t>
+  </si>
+  <si>
+    <t>Enodisomacris curtipennis</t>
+  </si>
+  <si>
+    <t>Erichius virgatus</t>
+  </si>
+  <si>
+    <t>Euathlus affinis</t>
+  </si>
+  <si>
+    <t>Eupsophus altor</t>
+  </si>
+  <si>
+    <t>Eupsophus contulmoensis</t>
+  </si>
+  <si>
+    <t>Eupsophus septentrionalis</t>
+  </si>
+  <si>
+    <t>Exallococcus laureliae</t>
+  </si>
+  <si>
+    <t>Falco sparverius fernandenzis</t>
+  </si>
+  <si>
+    <t>Fernandezia bulimoides</t>
+  </si>
+  <si>
+    <t>Fernandezia conifera</t>
+  </si>
+  <si>
+    <t>Fernandezia consimilis</t>
+  </si>
+  <si>
+    <t>Fernandezia cylindrella</t>
+  </si>
+  <si>
+    <t>Fernandezia diaphana</t>
+  </si>
+  <si>
+    <t>Fernandezia expansa</t>
+  </si>
+  <si>
+    <t>Fernandezia inornata</t>
+  </si>
+  <si>
+    <t>Fernandezia longa</t>
+  </si>
+  <si>
+    <t>Fernandezia philippiana</t>
+  </si>
+  <si>
+    <t>Fernandezia splendida</t>
+  </si>
+  <si>
+    <t>Fernandezia tryoni</t>
+  </si>
+  <si>
+    <t>Fernandezia wilsoni</t>
+  </si>
+  <si>
+    <t>Gyriosomus angustus</t>
+  </si>
+  <si>
+    <t>Heleobia ascotanensis</t>
+  </si>
+  <si>
+    <t>Henicotherus francisca</t>
+  </si>
+  <si>
+    <t>Homoeomma orellanai</t>
+  </si>
+  <si>
+    <t>Lasia pulla</t>
+  </si>
+  <si>
+    <t>Liolaemus carlosgarini</t>
+  </si>
+  <si>
+    <t>Liolaemus fabiani</t>
+  </si>
+  <si>
+    <t>Liolaemus foxi</t>
+  </si>
+  <si>
+    <t>Liolaemus frassinettii</t>
+  </si>
+  <si>
+    <t>Liolaemus leftrarui</t>
+  </si>
+  <si>
+    <t>Liolaemus leopardinus</t>
+  </si>
+  <si>
+    <t>Liolaemus manueli</t>
+  </si>
+  <si>
+    <t>Liolaemus nigrocoeruleus</t>
+  </si>
+  <si>
+    <t>Liolaemus scorialis</t>
+  </si>
+  <si>
+    <t>Liolaemus septentrionalis</t>
+  </si>
+  <si>
+    <t>Liolaemus thermarum</t>
+  </si>
+  <si>
+    <t>Liolaemus ubaghsi</t>
+  </si>
+  <si>
+    <t>Liolaemus villaricensis</t>
+  </si>
+  <si>
+    <t>Luispenaia paposo</t>
+  </si>
+  <si>
+    <t>Lycalopex fulvipes</t>
+  </si>
+  <si>
+    <t>Lynceus huentelauquensis</t>
+  </si>
+  <si>
+    <t>Mordacia lapicida</t>
+  </si>
+  <si>
+    <t>Nematogenys inermis</t>
+  </si>
+  <si>
+    <t>Neuquenaphis staryi</t>
+  </si>
+  <si>
+    <t>Nycterinus angusticollis</t>
+  </si>
+  <si>
+    <t>Nycterinus borealis</t>
+  </si>
+  <si>
+    <t>Nycterinus mannerheimi</t>
+  </si>
+  <si>
+    <t>Oogenius castilloi</t>
+  </si>
+  <si>
+    <t>Oogenius penai</t>
+  </si>
+  <si>
+    <t>Orestias ascotanensis</t>
+  </si>
+  <si>
+    <t>Orestias chungarensis</t>
+  </si>
+  <si>
+    <t>Orestias laucaensis</t>
+  </si>
+  <si>
+    <t>Orestias parinacotensis</t>
+  </si>
+  <si>
+    <t>Paropisthopatus umbrinus</t>
+  </si>
+  <si>
+    <t>Percilia gillissi</t>
+  </si>
+  <si>
+    <t>Percilia irwini</t>
+  </si>
+  <si>
+    <t>Phyllopetalia altarensis</t>
+  </si>
+  <si>
+    <t>Phymaturus bibronii</t>
+  </si>
+  <si>
+    <t>Phymaturus darwini</t>
+  </si>
+  <si>
+    <t>Phymaturus maulense</t>
+  </si>
+  <si>
+    <t>Plectostylus araucanus</t>
+  </si>
+  <si>
+    <t>Praocis aenea</t>
+  </si>
+  <si>
+    <t>Praocis bicentenario</t>
+  </si>
+  <si>
+    <t>Pristidactylus valeriae</t>
+  </si>
+  <si>
+    <t>Pristidactylus volcanensis</t>
+  </si>
+  <si>
+    <t>Ptychodon oculta</t>
+  </si>
+  <si>
+    <t>Ptychodon skottsberg</t>
+  </si>
+  <si>
+    <t>Scotobius planicosta</t>
+  </si>
+  <si>
+    <t>Succinea fragilis</t>
+  </si>
+  <si>
+    <t>Succinea mamillata</t>
+  </si>
+  <si>
+    <t>Succinea pinguis</t>
+  </si>
+  <si>
+    <t>Telmatobius philippii</t>
+  </si>
+  <si>
+    <t>Telmatobufo ignotus</t>
+  </si>
+  <si>
+    <t>Telmatobufo venustus</t>
+  </si>
+  <si>
+    <t>Tornatellina minuta</t>
+  </si>
+  <si>
+    <t>Trichomycterus laucaensis</t>
+  </si>
+  <si>
+    <t>Uretacris lilai</t>
+  </si>
+  <si>
+    <t>Valdiviomyia gigantea</t>
+  </si>
+  <si>
+    <t>Virilastacus rucapihuelensis</t>
+  </si>
+  <si>
+    <t>Chileputo chilensis</t>
+  </si>
+  <si>
+    <t>Alsodes barrioi</t>
+  </si>
+  <si>
+    <t>Alsodes montanus</t>
+  </si>
+  <si>
+    <t>Alsodes tumultuosus</t>
+  </si>
+  <si>
+    <t>Alsodes vanzolinii</t>
+  </si>
+  <si>
+    <t>Anairetes fernandezianus</t>
+  </si>
+  <si>
+    <t>Cheirodon kiliani</t>
+  </si>
+  <si>
+    <t>Diplomystes chilensis</t>
+  </si>
+  <si>
+    <t>Eupsophus insularis</t>
+  </si>
+  <si>
+    <t>Eupsophus migueli</t>
+  </si>
+  <si>
+    <t>Eupsophus nahuelbutensis</t>
+  </si>
+  <si>
+    <t>Galaxias globiceps</t>
+  </si>
+  <si>
+    <t>Insuetophrynus acarpicus</t>
+  </si>
+  <si>
+    <t>Telmatobius pefauri</t>
+  </si>
+  <si>
+    <t>Telmatobius zapahuirensis</t>
+  </si>
+  <si>
+    <t>Trichomycterus chiltoni</t>
+  </si>
+  <si>
+    <t>Trichomycterus chungaraensis</t>
+  </si>
+  <si>
+    <t>Trichomycterus rivulatus</t>
+  </si>
+  <si>
+    <t>Pancora</t>
+  </si>
+  <si>
+    <t>Mosca florícola de Juan Fernández</t>
+  </si>
+  <si>
+    <t>Sapo</t>
+  </si>
+  <si>
+    <t>Rana de pecho espinoso de Cordillera Pelada</t>
+  </si>
+  <si>
+    <t>Típula pintada</t>
+  </si>
+  <si>
+    <t>Liguay, sanguijuela gigante valdiviana</t>
+  </si>
+  <si>
+    <t>Caracol terrestre Amphidoxa</t>
+  </si>
+  <si>
+    <t>Peladilla</t>
+  </si>
+  <si>
+    <t>Mancapollo, pica pollo, borracho, borrachito, buey</t>
+  </si>
+  <si>
+    <t>Pejerrey</t>
+  </si>
+  <si>
+    <t>Escarabajo</t>
+  </si>
+  <si>
+    <t>Escorpión de Cepeda</t>
+  </si>
+  <si>
+    <t>Bagrecito</t>
+  </si>
+  <si>
+    <t>Cascarudo de Cantillana</t>
+  </si>
+  <si>
+    <t>Cascarudo de Las Docas</t>
+  </si>
+  <si>
+    <t>Cascarudo de Peña</t>
+  </si>
+  <si>
+    <t>Cascarudo de la Plata</t>
+  </si>
+  <si>
+    <t>Caracol terrestre Charopa</t>
+  </si>
+  <si>
+    <t>Chinchilla costina</t>
+  </si>
+  <si>
+    <t>Balita, insecto joya de Fisher</t>
+  </si>
+  <si>
+    <t>Balita, insecto joya de Leech</t>
+  </si>
+  <si>
+    <t>Tollo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tollo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langosta de alas cortas; langosta de Ureta; langosta de Lila; langosta de La Chimba
+</t>
+  </si>
+  <si>
+    <t>Borrachito de Tolhuaca, borrachito listado de Tolhuaca</t>
+  </si>
+  <si>
+    <t>Tarántula afín de Santiago</t>
+  </si>
+  <si>
+    <t>Rana de hojarasca de Oncol</t>
+  </si>
+  <si>
+    <t>Sapo de Contulmo</t>
+  </si>
+  <si>
+    <t>Ranita de Los Queules</t>
+  </si>
+  <si>
+    <t>Cochinilla de fieltro (genérico)</t>
+  </si>
+  <si>
+    <t>Cernícalo de Juan Fernández</t>
+  </si>
+  <si>
+    <t>Caracol terrestre de Juan Fernández</t>
+  </si>
+  <si>
+    <t>Vaquita del desierto de Paposo</t>
+  </si>
+  <si>
+    <t>Caracol</t>
+  </si>
+  <si>
+    <t>No conocido</t>
+  </si>
+  <si>
+    <t>Tarántula enana de penacho amarillo, araña pollito</t>
+  </si>
+  <si>
+    <t>Mosca colibrí enana</t>
+  </si>
+  <si>
+    <t>Lagartija de Garín</t>
+  </si>
+  <si>
+    <t>Lagartija de Fabián</t>
+  </si>
+  <si>
+    <t>Lagartija de Fox</t>
+  </si>
+  <si>
+    <t>Lagartija del Cerro Cantillana, lagarto de Frassinetti</t>
+  </si>
+  <si>
+    <t>Lagartija de Leftraru, Leftraru’s Lizard (Inglés)</t>
+  </si>
+  <si>
+    <t>Lagarto leopardo</t>
+  </si>
+  <si>
+    <t>Lagartija de Manuel</t>
+  </si>
+  <si>
+    <t>Lagartija negro azulada, Black Bluish Lizard (Inglés)</t>
+  </si>
+  <si>
+    <t>Lagarto del escorial, Slag Lizard (Inglés)</t>
+  </si>
+  <si>
+    <t>Lagartija pintada septentrional, Northern Painted Lizard (Inglés)</t>
+  </si>
+  <si>
+    <t>Lagartija del Azufre</t>
+  </si>
+  <si>
+    <t>Lagarto leopardo de Ubaghs, Ubaghs’ Leopard Lizard (Inglés)</t>
+  </si>
+  <si>
+    <t>Lagartija</t>
+  </si>
+  <si>
+    <t>Pololo de Paposo</t>
+  </si>
+  <si>
+    <t>Zorro de Chiloé</t>
+  </si>
+  <si>
+    <t>Camarón almeja de Huentelauquén</t>
+  </si>
+  <si>
+    <t>Lamprea de agua dulce</t>
+  </si>
+  <si>
+    <t>Bagre grande</t>
+  </si>
+  <si>
+    <t>No tiene, se propone "pulgón del Ruíl"</t>
+  </si>
+  <si>
+    <t>Insecto joya</t>
+  </si>
+  <si>
+    <t>Cucaracho negro</t>
+  </si>
+  <si>
+    <t>Tenebrio de Mannerheim, teatino de Mannerheim</t>
+  </si>
+  <si>
+    <t>Karachi, orestias</t>
+  </si>
+  <si>
+    <t>Gusano aterciopelado, onicóforo (genérico)</t>
+  </si>
+  <si>
+    <t>Carmelita</t>
+  </si>
+  <si>
+    <t>Carmelita de Concepción</t>
+  </si>
+  <si>
+    <t>Matuasto de Bibron</t>
+  </si>
+  <si>
+    <t>Matuasto de Darwin, lagarto de cola gruesa</t>
+  </si>
+  <si>
+    <t>Matuasto</t>
+  </si>
+  <si>
+    <t>Caracol de árbol araucano, caracol de árbol</t>
+  </si>
+  <si>
+    <t>Vaquita</t>
+  </si>
+  <si>
+    <t>Vaquita del bicentenario</t>
+  </si>
+  <si>
+    <t>Gruñidor de Valeria</t>
+  </si>
+  <si>
+    <t>Gruñidor de El Volcán</t>
+  </si>
+  <si>
+    <t>Caracol terrestre Ptychodon</t>
+  </si>
+  <si>
+    <t>Caracol terrestre Succinea</t>
+  </si>
+  <si>
+    <t>Sapo de Philippi</t>
+  </si>
+  <si>
+    <t>Rana montana de Los Queules</t>
+  </si>
+  <si>
+    <t>Sapo hermoso</t>
+  </si>
+  <si>
+    <t>Caracol terrestre Tornatellina</t>
+  </si>
+  <si>
+    <t>Langosta de Ureta, langosta de Lila, langosta de La Chimba</t>
+  </si>
+  <si>
+    <t>Mosca florícola valdiviana gigante</t>
+  </si>
+  <si>
+    <t>Camarón</t>
+  </si>
+  <si>
+    <t>Chanchito blanco de la araucaria</t>
+  </si>
+  <si>
+    <t>Sapo de Barros</t>
+  </si>
+  <si>
+    <t>Sapo de monte</t>
+  </si>
+  <si>
+    <t>Sapo de Vanzolini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cachudito de Juan Fernández </t>
+  </si>
+  <si>
+    <t>Pocha</t>
+  </si>
+  <si>
+    <t>Tollo de agua dulce</t>
+  </si>
+  <si>
+    <t>Sapo de Isla Mocha</t>
+  </si>
+  <si>
+    <t>Sapo de Miguel</t>
+  </si>
+  <si>
+    <t>Sapo de Nahuelbuta</t>
+  </si>
+  <si>
+    <t>Puye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sapo </t>
+  </si>
+  <si>
+    <t>Sapo de Pefaur</t>
+  </si>
+  <si>
+    <t>Sapo de Zapahuira</t>
+  </si>
+  <si>
+    <t>Arachnida</t>
+  </si>
+  <si>
+    <t>Malacostraca</t>
+  </si>
+  <si>
+    <t>Amphibia</t>
+  </si>
+  <si>
+    <t>Gastropoda</t>
+  </si>
+  <si>
+    <t>Aves</t>
+  </si>
+  <si>
+    <t>Insecta</t>
+  </si>
+  <si>
+    <t>Gasotropoda</t>
+  </si>
+  <si>
+    <t>Reptilia</t>
+  </si>
+  <si>
+    <t>Actinopterygii</t>
+  </si>
+  <si>
+    <t>Anthozoa</t>
+  </si>
+  <si>
+    <t>Clitellata</t>
+  </si>
+  <si>
+    <t>Mammalia</t>
+  </si>
+  <si>
+    <t>Branchiopoda</t>
+  </si>
+  <si>
+    <t>Cephalaspidomorphi</t>
+  </si>
+  <si>
+    <t>Udeonycophora</t>
+  </si>
+  <si>
+    <t>Noticias únicas</t>
+  </si>
+  <si>
+    <t>RCE</t>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>EN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EN </t>
+  </si>
+  <si>
+    <t>EN-RARA</t>
+  </si>
+  <si>
+    <t>Alcance</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,6 +1194,25 @@
     <font>
       <sz val="11"/>
       <name val="CG Times (W1)"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -466,8 +1236,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -487,17 +1280,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{82CB6572-404C-4904-BAE7-246A6D6E0301}" name="Tabla24" displayName="Tabla24" ref="A1:L71" totalsRowShown="0">
-  <autoFilter ref="A1:L71" xr:uid="{82CB6572-404C-4904-BAE7-246A6D6E0301}"/>
-  <tableColumns count="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{82CB6572-404C-4904-BAE7-246A6D6E0301}" name="Tabla24" displayName="Tabla24" ref="A1:M207" totalsRowShown="0">
+  <autoFilter ref="A1:M207" xr:uid="{82CB6572-404C-4904-BAE7-246A6D6E0301}"/>
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{D8CAA665-70A5-4AC5-B2CE-C73831F0D97F}" name="Especie ID"/>
     <tableColumn id="2" xr3:uid="{D12C8A28-44BD-4FDC-AE75-BA1C64FD3D76}" name="Nombre científico "/>
     <tableColumn id="3" xr3:uid="{5FD2AE46-9541-440A-901F-E328FE474AF7}" name="Nombre común"/>
     <tableColumn id="4" xr3:uid="{9D94CF3B-E776-4470-9B80-935EA4AB088E}" name="Clase"/>
+    <tableColumn id="16" xr3:uid="{9EDA8F6B-56C5-42DC-9732-EBA28F85C9DC}" name="RCE"/>
     <tableColumn id="5" xr3:uid="{76FD7BBB-E817-4A87-8A0F-374E5C1A4875}" name="Usa N. Científico"/>
     <tableColumn id="13" xr3:uid="{3D0CC132-8F95-49D3-A61F-98BEAD9D8D16}" name="Usa N. Común"/>
-    <tableColumn id="6" xr3:uid="{FA6967FF-3902-4A8C-915D-15C025F76AD4}" name="Mención nacional"/>
-    <tableColumn id="7" xr3:uid="{91C979A9-CDDC-48F6-AAAB-2029D6C53C93}" name="Mención regional"/>
+    <tableColumn id="14" xr3:uid="{458F0D42-9957-477C-BBAC-A92EE3098B53}" name="Noticias únicas"/>
+    <tableColumn id="7" xr3:uid="{91C979A9-CDDC-48F6-AAAB-2029D6C53C93}" name="Alcance"/>
     <tableColumn id="12" xr3:uid="{EDC1753B-0323-4A81-9585-86B6CFC0A5F6}" name="Es carismático"/>
     <tableColumn id="8" xr3:uid="{D4874694-5509-4579-8FEA-EEB1181091DD}" name="Es protagonsita"/>
     <tableColumn id="9" xr3:uid="{4CF373DE-A10B-4D79-BEB7-F277ECB6A0AF}" name="Tiene foto"/>
@@ -824,22 +1618,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15770910-20FF-40BA-B5C9-C288585D5722}">
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:M207"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="26.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -853,31 +1649,34 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>128</v>
+        <v>374</v>
       </c>
       <c r="F1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H1" t="s">
-        <v>127</v>
+        <v>373</v>
       </c>
       <c r="I1" t="s">
+        <v>379</v>
+      </c>
+      <c r="J1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>1</v>
       </c>
@@ -887,8 +1686,14 @@
       <c r="C2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="D2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>2</v>
       </c>
@@ -898,8 +1703,14 @@
       <c r="C3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="D3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>3</v>
       </c>
@@ -909,8 +1720,14 @@
       <c r="C4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="D4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>4</v>
       </c>
@@ -920,8 +1737,14 @@
       <c r="C5" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="D5" t="s">
+        <v>360</v>
+      </c>
+      <c r="E5" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>5</v>
       </c>
@@ -931,8 +1754,14 @@
       <c r="C6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="D6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>6</v>
       </c>
@@ -942,8 +1771,14 @@
       <c r="C7" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="D7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>7</v>
       </c>
@@ -953,8 +1788,14 @@
       <c r="C8" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="D8" t="s">
+        <v>361</v>
+      </c>
+      <c r="E8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>8</v>
       </c>
@@ -964,8 +1805,14 @@
       <c r="C9" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="D9" t="s">
+        <v>358</v>
+      </c>
+      <c r="E9" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>9</v>
       </c>
@@ -975,8 +1822,14 @@
       <c r="C10" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="D10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E10" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>10</v>
       </c>
@@ -986,8 +1839,14 @@
       <c r="C11" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="D11" t="s">
+        <v>361</v>
+      </c>
+      <c r="E11" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>11</v>
       </c>
@@ -997,8 +1856,14 @@
       <c r="C12" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="D12" t="s">
+        <v>358</v>
+      </c>
+      <c r="E12" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1008,8 +1873,14 @@
       <c r="C13" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="D13" t="s">
+        <v>363</v>
+      </c>
+      <c r="E13" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1019,8 +1890,14 @@
       <c r="C14" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="D14" t="s">
+        <v>363</v>
+      </c>
+      <c r="E14" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1030,8 +1907,14 @@
       <c r="C15" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="D15" t="s">
+        <v>358</v>
+      </c>
+      <c r="E15" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1041,8 +1924,14 @@
       <c r="C16" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>361</v>
+      </c>
+      <c r="E16" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1052,8 +1941,14 @@
       <c r="C17" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>363</v>
+      </c>
+      <c r="E17" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1063,16 +1958,28 @@
       <c r="C18" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>364</v>
+      </c>
+      <c r="E18" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>363</v>
+      </c>
+      <c r="E19" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1082,8 +1989,14 @@
       <c r="C20" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" t="s">
+        <v>363</v>
+      </c>
+      <c r="E20" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1093,8 +2006,14 @@
       <c r="C21" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" t="s">
+        <v>363</v>
+      </c>
+      <c r="E21" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1104,8 +2023,14 @@
       <c r="C22" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" t="s">
+        <v>358</v>
+      </c>
+      <c r="E22" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1115,8 +2040,14 @@
       <c r="C23" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" t="s">
+        <v>358</v>
+      </c>
+      <c r="E23" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1126,8 +2057,14 @@
       <c r="C24" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" t="s">
+        <v>358</v>
+      </c>
+      <c r="E24" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1137,8 +2074,14 @@
       <c r="C25" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" t="s">
+        <v>358</v>
+      </c>
+      <c r="E25" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1148,8 +2091,14 @@
       <c r="C26" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" t="s">
+        <v>362</v>
+      </c>
+      <c r="E26" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1159,8 +2108,14 @@
       <c r="C27" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27" t="s">
+        <v>362</v>
+      </c>
+      <c r="E27" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1170,8 +2125,14 @@
       <c r="C28" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28" t="s">
+        <v>361</v>
+      </c>
+      <c r="E28" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1181,8 +2142,14 @@
       <c r="C29" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29" t="s">
+        <v>361</v>
+      </c>
+      <c r="E29" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1192,8 +2159,14 @@
       <c r="C30" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30" t="s">
+        <v>365</v>
+      </c>
+      <c r="E30" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1203,8 +2176,14 @@
       <c r="C31" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="D31" t="s">
+        <v>365</v>
+      </c>
+      <c r="E31" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1214,8 +2193,14 @@
       <c r="C32" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32" t="s">
+        <v>365</v>
+      </c>
+      <c r="E32" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1225,8 +2210,14 @@
       <c r="C33" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33" t="s">
+        <v>365</v>
+      </c>
+      <c r="E33" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1236,16 +2227,28 @@
       <c r="C34" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34" t="s">
+        <v>365</v>
+      </c>
+      <c r="E34" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="D35" t="s">
+        <v>363</v>
+      </c>
+      <c r="E35" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1255,8 +2258,14 @@
       <c r="C36" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="D36" t="s">
+        <v>363</v>
+      </c>
+      <c r="E36" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1266,8 +2275,14 @@
       <c r="C37" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="D37" t="s">
+        <v>361</v>
+      </c>
+      <c r="E37" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1277,8 +2292,14 @@
       <c r="C38" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="D38" t="s">
+        <v>366</v>
+      </c>
+      <c r="E38" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1288,8 +2309,14 @@
       <c r="C39" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="D39" t="s">
+        <v>366</v>
+      </c>
+      <c r="E39" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1299,16 +2326,28 @@
       <c r="C40" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="D40" t="s">
+        <v>363</v>
+      </c>
+      <c r="E40" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="D41" t="s">
+        <v>363</v>
+      </c>
+      <c r="E41" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1318,8 +2357,14 @@
       <c r="C42" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="D42" t="s">
+        <v>365</v>
+      </c>
+      <c r="E42" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1329,8 +2374,14 @@
       <c r="C43" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="D43" t="s">
+        <v>365</v>
+      </c>
+      <c r="E43" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1340,16 +2391,28 @@
       <c r="C44" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
+      <c r="D44" t="s">
+        <v>361</v>
+      </c>
+      <c r="E44" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="D45" t="s">
+        <v>363</v>
+      </c>
+      <c r="E45" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1359,8 +2422,14 @@
       <c r="C46" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="D46" t="s">
+        <v>365</v>
+      </c>
+      <c r="E46" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1370,8 +2439,14 @@
       <c r="C47" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="D47" t="s">
+        <v>366</v>
+      </c>
+      <c r="E47" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1381,8 +2456,14 @@
       <c r="C48" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
+      <c r="D48" t="s">
+        <v>361</v>
+      </c>
+      <c r="E48" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1392,8 +2473,14 @@
       <c r="C49" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
+      <c r="D49" t="s">
+        <v>361</v>
+      </c>
+      <c r="E49" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1403,8 +2490,14 @@
       <c r="C50" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
+      <c r="D50" t="s">
+        <v>360</v>
+      </c>
+      <c r="E50" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1414,8 +2507,14 @@
       <c r="C51" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
+      <c r="D51" t="s">
+        <v>363</v>
+      </c>
+      <c r="E51" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1425,8 +2524,14 @@
       <c r="C52" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
+      <c r="D52" t="s">
+        <v>362</v>
+      </c>
+      <c r="E52" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1436,8 +2541,14 @@
       <c r="C53" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
+      <c r="D53" t="s">
+        <v>363</v>
+      </c>
+      <c r="E53" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1447,8 +2558,14 @@
       <c r="C54" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
+      <c r="D54" t="s">
+        <v>361</v>
+      </c>
+      <c r="E54" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1458,8 +2575,14 @@
       <c r="C55" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
+      <c r="D55" t="s">
+        <v>361</v>
+      </c>
+      <c r="E55" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1469,8 +2592,14 @@
       <c r="C56" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
+      <c r="D56" t="s">
+        <v>361</v>
+      </c>
+      <c r="E56" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1480,8 +2609,14 @@
       <c r="C57" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
+      <c r="D57" t="s">
+        <v>361</v>
+      </c>
+      <c r="E57" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1491,8 +2626,14 @@
       <c r="C58" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
+      <c r="D58" t="s">
+        <v>361</v>
+      </c>
+      <c r="E58" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1502,8 +2643,14 @@
       <c r="C59" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
+      <c r="D59" t="s">
+        <v>361</v>
+      </c>
+      <c r="E59" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1513,8 +2660,14 @@
       <c r="C60" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
+      <c r="D60" t="s">
+        <v>361</v>
+      </c>
+      <c r="E60" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1524,8 +2677,14 @@
       <c r="C61" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
+      <c r="D61" t="s">
+        <v>367</v>
+      </c>
+      <c r="E61" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1535,8 +2694,14 @@
       <c r="C62" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="63" spans="1:3">
+      <c r="D62" t="s">
+        <v>360</v>
+      </c>
+      <c r="E62" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1546,8 +2711,14 @@
       <c r="C63" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="64" spans="1:3">
+      <c r="D63" t="s">
+        <v>360</v>
+      </c>
+      <c r="E63" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1557,8 +2728,14 @@
       <c r="C64" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
+      <c r="D64" t="s">
+        <v>360</v>
+      </c>
+      <c r="E64" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1568,8 +2745,14 @@
       <c r="C65" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
+      <c r="D65" t="s">
+        <v>360</v>
+      </c>
+      <c r="E65" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1579,8 +2762,14 @@
       <c r="C66" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
+      <c r="D66" t="s">
+        <v>360</v>
+      </c>
+      <c r="E66" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1590,8 +2779,14 @@
       <c r="C67" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="D67" t="s">
+        <v>361</v>
+      </c>
+      <c r="E67" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1601,8 +2796,14 @@
       <c r="C68" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="69" spans="1:3">
+      <c r="D68" t="s">
+        <v>361</v>
+      </c>
+      <c r="E68" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1612,8 +2813,14 @@
       <c r="C69" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
+      <c r="D69" t="s">
+        <v>361</v>
+      </c>
+      <c r="E69" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1623,8 +2830,14 @@
       <c r="C70" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
+      <c r="D70" t="s">
+        <v>361</v>
+      </c>
+      <c r="E70" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1633,6 +2846,2310 @@
       </c>
       <c r="C71" t="s">
         <v>125</v>
+      </c>
+      <c r="D71" t="s">
+        <v>361</v>
+      </c>
+      <c r="E71" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C72" s="5"/>
+      <c r="D72" t="s">
+        <v>363</v>
+      </c>
+      <c r="E72" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D73" t="s">
+        <v>359</v>
+      </c>
+      <c r="E73" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D74" t="s">
+        <v>359</v>
+      </c>
+      <c r="E74" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D75" t="s">
+        <v>359</v>
+      </c>
+      <c r="E75" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D76" t="s">
+        <v>359</v>
+      </c>
+      <c r="E76" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D77" t="s">
+        <v>359</v>
+      </c>
+      <c r="E77" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D78" t="s">
+        <v>359</v>
+      </c>
+      <c r="E78" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D79" t="s">
+        <v>363</v>
+      </c>
+      <c r="E79" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D80" t="s">
+        <v>360</v>
+      </c>
+      <c r="E80" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="D81" t="s">
+        <v>360</v>
+      </c>
+      <c r="E81" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="D82" t="s">
+        <v>363</v>
+      </c>
+      <c r="E82" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="D83" t="s">
+        <v>368</v>
+      </c>
+      <c r="E83" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D84" t="s">
+        <v>361</v>
+      </c>
+      <c r="E84" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D85" t="s">
+        <v>361</v>
+      </c>
+      <c r="E85" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D86" t="s">
+        <v>361</v>
+      </c>
+      <c r="E86" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D87" t="s">
+        <v>361</v>
+      </c>
+      <c r="E87" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D88" t="s">
+        <v>361</v>
+      </c>
+      <c r="E88" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D89" t="s">
+        <v>361</v>
+      </c>
+      <c r="E89" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D90" t="s">
+        <v>361</v>
+      </c>
+      <c r="E90" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D91" t="s">
+        <v>361</v>
+      </c>
+      <c r="E91" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="D92" t="s">
+        <v>366</v>
+      </c>
+      <c r="E92" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D93" t="s">
+        <v>363</v>
+      </c>
+      <c r="E93" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D94" t="s">
+        <v>366</v>
+      </c>
+      <c r="E94" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D95" t="s">
+        <v>363</v>
+      </c>
+      <c r="E95" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="D96" t="s">
+        <v>358</v>
+      </c>
+      <c r="E96" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D97" t="s">
+        <v>366</v>
+      </c>
+      <c r="E97" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D98" t="s">
+        <v>363</v>
+      </c>
+      <c r="E98" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D99" t="s">
+        <v>363</v>
+      </c>
+      <c r="E99" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D100" t="s">
+        <v>363</v>
+      </c>
+      <c r="E100" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="D101" t="s">
+        <v>363</v>
+      </c>
+      <c r="E101" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D102" t="s">
+        <v>361</v>
+      </c>
+      <c r="E102" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D103" t="s">
+        <v>361</v>
+      </c>
+      <c r="E103" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D104" t="s">
+        <v>369</v>
+      </c>
+      <c r="E104" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C105" s="5"/>
+      <c r="D105" t="s">
+        <v>363</v>
+      </c>
+      <c r="E105" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C106" s="5"/>
+      <c r="D106" t="s">
+        <v>363</v>
+      </c>
+      <c r="E106" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D107" t="s">
+        <v>363</v>
+      </c>
+      <c r="E107" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D108" t="s">
+        <v>363</v>
+      </c>
+      <c r="E108" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D109" t="s">
+        <v>366</v>
+      </c>
+      <c r="E109" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="D110" t="s">
+        <v>366</v>
+      </c>
+      <c r="E110" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="29">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D111" t="s">
+        <v>363</v>
+      </c>
+      <c r="E111" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="D112" t="s">
+        <v>363</v>
+      </c>
+      <c r="E112" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D113" t="s">
+        <v>358</v>
+      </c>
+      <c r="E113" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D114" t="s">
+        <v>360</v>
+      </c>
+      <c r="E114" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="D115" t="s">
+        <v>360</v>
+      </c>
+      <c r="E115" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D116" t="s">
+        <v>360</v>
+      </c>
+      <c r="E116" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="D117" t="s">
+        <v>363</v>
+      </c>
+      <c r="E117" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D118" t="s">
+        <v>362</v>
+      </c>
+      <c r="E118" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D119" t="s">
+        <v>361</v>
+      </c>
+      <c r="E119" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D120" t="s">
+        <v>361</v>
+      </c>
+      <c r="E120" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D121" t="s">
+        <v>361</v>
+      </c>
+      <c r="E121" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D122" t="s">
+        <v>361</v>
+      </c>
+      <c r="E122" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D123" t="s">
+        <v>361</v>
+      </c>
+      <c r="E123" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D124" t="s">
+        <v>361</v>
+      </c>
+      <c r="E124" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D125" t="s">
+        <v>361</v>
+      </c>
+      <c r="E125" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D126" t="s">
+        <v>361</v>
+      </c>
+      <c r="E126" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D127" t="s">
+        <v>361</v>
+      </c>
+      <c r="E127" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D128" t="s">
+        <v>361</v>
+      </c>
+      <c r="E128" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D129" t="s">
+        <v>361</v>
+      </c>
+      <c r="E129" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D130" t="s">
+        <v>361</v>
+      </c>
+      <c r="E130" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D131" t="s">
+        <v>363</v>
+      </c>
+      <c r="E131" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D132" t="s">
+        <v>361</v>
+      </c>
+      <c r="E132" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="D133" t="s">
+        <v>363</v>
+      </c>
+      <c r="E133" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D134" t="s">
+        <v>358</v>
+      </c>
+      <c r="E134" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D135" t="s">
+        <v>363</v>
+      </c>
+      <c r="E135" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D136" t="s">
+        <v>365</v>
+      </c>
+      <c r="E136" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D137" t="s">
+        <v>365</v>
+      </c>
+      <c r="E137" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D138" t="s">
+        <v>365</v>
+      </c>
+      <c r="E138" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D139" t="s">
+        <v>365</v>
+      </c>
+      <c r="E139" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="D140" t="s">
+        <v>365</v>
+      </c>
+      <c r="E140" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="D141" t="s">
+        <v>365</v>
+      </c>
+      <c r="E141" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D142" t="s">
+        <v>365</v>
+      </c>
+      <c r="E142" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D143" t="s">
+        <v>365</v>
+      </c>
+      <c r="E143" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D144" t="s">
+        <v>365</v>
+      </c>
+      <c r="E144" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="D145" t="s">
+        <v>365</v>
+      </c>
+      <c r="E145" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D146" t="s">
+        <v>365</v>
+      </c>
+      <c r="E146" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D147" t="s">
+        <v>365</v>
+      </c>
+      <c r="E147" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="D148" t="s">
+        <v>365</v>
+      </c>
+      <c r="E148" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="D149" t="s">
+        <v>363</v>
+      </c>
+      <c r="E149" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="D150" t="s">
+        <v>369</v>
+      </c>
+      <c r="E150" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D151" t="s">
+        <v>370</v>
+      </c>
+      <c r="E151" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D152" t="s">
+        <v>371</v>
+      </c>
+      <c r="E152" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D153" t="s">
+        <v>366</v>
+      </c>
+      <c r="E153" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="D154" t="s">
+        <v>363</v>
+      </c>
+      <c r="E154" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="D155" t="s">
+        <v>363</v>
+      </c>
+      <c r="E155" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="D156" t="s">
+        <v>363</v>
+      </c>
+      <c r="E156" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="D157" t="s">
+        <v>363</v>
+      </c>
+      <c r="E157" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C158" s="5"/>
+      <c r="D158" t="s">
+        <v>363</v>
+      </c>
+      <c r="E158" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C159" s="5"/>
+      <c r="D159" t="s">
+        <v>363</v>
+      </c>
+      <c r="E159" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D160" t="s">
+        <v>366</v>
+      </c>
+      <c r="E160" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D161" t="s">
+        <v>366</v>
+      </c>
+      <c r="E161" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D162" t="s">
+        <v>366</v>
+      </c>
+      <c r="E162" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D163" t="s">
+        <v>366</v>
+      </c>
+      <c r="E163" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="D164" t="s">
+        <v>372</v>
+      </c>
+      <c r="E164" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="D165" t="s">
+        <v>366</v>
+      </c>
+      <c r="E165" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="D166" t="s">
+        <v>366</v>
+      </c>
+      <c r="E166" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C167" s="6"/>
+      <c r="D167" t="s">
+        <v>363</v>
+      </c>
+      <c r="E167" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D168" t="s">
+        <v>365</v>
+      </c>
+      <c r="E168" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D169" t="s">
+        <v>365</v>
+      </c>
+      <c r="E169" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D170" t="s">
+        <v>365</v>
+      </c>
+      <c r="E170" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="D171" t="s">
+        <v>361</v>
+      </c>
+      <c r="E171" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D172" t="s">
+        <v>363</v>
+      </c>
+      <c r="E172" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="D173" t="s">
+        <v>363</v>
+      </c>
+      <c r="E173" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="D174" t="s">
+        <v>365</v>
+      </c>
+      <c r="E174" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="D175" t="s">
+        <v>365</v>
+      </c>
+      <c r="E175" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D176" t="s">
+        <v>361</v>
+      </c>
+      <c r="E176" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D177" t="s">
+        <v>361</v>
+      </c>
+      <c r="E177" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C178" s="6"/>
+      <c r="D178" t="s">
+        <v>363</v>
+      </c>
+      <c r="E178" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D179" t="s">
+        <v>361</v>
+      </c>
+      <c r="E179" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D180" t="s">
+        <v>361</v>
+      </c>
+      <c r="E180" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D181" t="s">
+        <v>361</v>
+      </c>
+      <c r="E181" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D182" t="s">
+        <v>360</v>
+      </c>
+      <c r="E182" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="D183" t="s">
+        <v>360</v>
+      </c>
+      <c r="E183" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="D184" t="s">
+        <v>360</v>
+      </c>
+      <c r="E184" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="D185" t="s">
+        <v>361</v>
+      </c>
+      <c r="E185" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D186" t="s">
+        <v>366</v>
+      </c>
+      <c r="E186" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="D187" t="s">
+        <v>363</v>
+      </c>
+      <c r="E187" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="D188" t="s">
+        <v>363</v>
+      </c>
+      <c r="E188" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="D189" t="s">
+        <v>359</v>
+      </c>
+      <c r="E189" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D190" t="s">
+        <v>363</v>
+      </c>
+      <c r="E190" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="D191" t="s">
+        <v>360</v>
+      </c>
+      <c r="E191" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="D192" t="s">
+        <v>360</v>
+      </c>
+      <c r="E192" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D193" t="s">
+        <v>360</v>
+      </c>
+      <c r="E193" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="D194" t="s">
+        <v>360</v>
+      </c>
+      <c r="E194" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="D195" t="s">
+        <v>362</v>
+      </c>
+      <c r="E195" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="D196" t="s">
+        <v>366</v>
+      </c>
+      <c r="E196" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D197" t="s">
+        <v>366</v>
+      </c>
+      <c r="E197" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D198" t="s">
+        <v>360</v>
+      </c>
+      <c r="E198" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="D199" t="s">
+        <v>360</v>
+      </c>
+      <c r="E199" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="D200" t="s">
+        <v>360</v>
+      </c>
+      <c r="E200" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D201" t="s">
+        <v>366</v>
+      </c>
+      <c r="E201" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="D202" t="s">
+        <v>360</v>
+      </c>
+      <c r="E202" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="D203" t="s">
+        <v>360</v>
+      </c>
+      <c r="E203" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="D204" t="s">
+        <v>360</v>
+      </c>
+      <c r="E204" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D205" t="s">
+        <v>366</v>
+      </c>
+      <c r="E205" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D206" t="s">
+        <v>366</v>
+      </c>
+      <c r="E206" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C207" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D207" t="s">
+        <v>366</v>
+      </c>
+      <c r="E207" t="s">
+        <v>378</v>
       </c>
     </row>
   </sheetData>
